--- a/examples/excel/charts.xlsx
+++ b/examples/excel/charts.xlsx
@@ -3,9 +3,9 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Analysis" sheetId="2" r:id="R6d99d2bb90674f4d"/>
-    <x:sheet name="StockData" sheetId="3" r:id="Rd74c666890db4e2c"/>
-    <x:sheet name="Assessment" sheetId="4" r:id="R3215b0dc90284e3c"/>
+    <x:sheet name="Analysis" sheetId="2" r:id="R2db11f37d59a49d6"/>
+    <x:sheet name="StockData" sheetId="3" r:id="R7a596fc7efd2401b"/>
+    <x:sheet name="Assessment" sheetId="4" r:id="R2dff24d9725349a6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1825,7 +1825,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R84fa0330b9c54c8a"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R8aa6a3c3fbda4eda"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1855,7 +1855,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R54c73a221043425d"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rf546dfa5dfe4441c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1885,7 +1885,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R2b3c757b710d45d8"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Ra8274f169729443f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1915,7 +1915,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rda73f4fbbbe247b0"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R63b5e80eec464537"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1950,7 +1950,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Ra017d2f9d5b34719"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rc2c126b06bdc4b10"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1980,7 +1980,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R89e07cf0af2242f9"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R104f8ac61bb245fb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2015,7 +2015,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R9529ddd8bacd480c"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R6e17a72024e1448b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2050,7 +2050,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R15fb3cc363264bfa"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R006d030d87004d66"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2060,7 +2060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="str">
@@ -2323,12 +2323,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50de8eb6671543ca"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07dbeb937e1d44d8"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="11" t="str">
@@ -2555,12 +2555,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29dfdd3016224c64"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292b805f1e244275"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="12" t="str">
@@ -2983,12 +2983,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d422a2167fe4665"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb49ea258636e4eca"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="19" t="str">
@@ -3117,6 +3117,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2596108e5d724f21"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1da0d769c824469d"/>
 </x:worksheet>
 </file>